--- a/data/trans_bre/P2A_R-Edad-trans_bre.xlsx
+++ b/data/trans_bre/P2A_R-Edad-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-12,35; 10,28</t>
+          <t>-13,14; 8,78</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-14,48; 6,41</t>
+          <t>-13,75; 6,6</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-14,77; 5,26</t>
+          <t>-15,07; 4,92</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-3,16; 16,92</t>
+          <t>-3,65; 17,47</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-34,54; 42,38</t>
+          <t>-35,45; 34,86</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-36,34; 21,6</t>
+          <t>-34,72; 23,02</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-40,61; 21,01</t>
+          <t>-41,21; 19,29</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-3,65; 23,1</t>
+          <t>-4,14; 24,08</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-11,68; 3,96</t>
+          <t>-12,37; 2,69</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-3,87; 12,82</t>
+          <t>-2,92; 13,23</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-8,98; 6,77</t>
+          <t>-7,71; 7,61</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-9,36; 6,52</t>
+          <t>-8,86; 7,08</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-30,5; 12,77</t>
+          <t>-32,56; 8,57</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-11,48; 50,69</t>
+          <t>-8,58; 50,97</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-27,29; 24,88</t>
+          <t>-23,26; 30,19</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-11,34; 8,77</t>
+          <t>-11,11; 9,56</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-14,86; 8,57</t>
+          <t>-15,39; 8,69</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-10,59; 11,95</t>
+          <t>-11,43; 11,83</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-13,61; 5,55</t>
+          <t>-13,88; 5,65</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-3,81; 11,44</t>
+          <t>-4,26; 11,94</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-33,2; 24,23</t>
+          <t>-33,74; 24,18</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-23,78; 35,24</t>
+          <t>-24,5; 35,98</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-33,07; 17,77</t>
+          <t>-32,97; 18,25</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-4,81; 15,81</t>
+          <t>-5,36; 16,54</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-16,28; 2,23</t>
+          <t>-15,12; 3,14</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-13,09; 5,99</t>
+          <t>-13,42; 7,34</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,05; 21,08</t>
+          <t>1,68; 22,2</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-7,53; 13,06</t>
+          <t>-6,57; 14,26</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-34,86; 5,93</t>
+          <t>-32,71; 8,1</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-29,03; 17,16</t>
+          <t>-29,06; 22,15</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,44; 68,59</t>
+          <t>3,87; 74,96</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-9,57; 20,09</t>
+          <t>-8,79; 21,41</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-9,27; 0,33</t>
+          <t>-9,33; -0,18</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-4,78; 5,1</t>
+          <t>-4,85; 4,83</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-4,09; 5,22</t>
+          <t>-4,17; 5,38</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-2,4; 7,67</t>
+          <t>-2,63; 7,88</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-23,54; 1,02</t>
+          <t>-23,34; -0,03</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-12,67; 15,46</t>
+          <t>-12,81; 14,58</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-11,5; 16,36</t>
+          <t>-11,57; 17,29</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-3,09; 10,43</t>
+          <t>-3,38; 10,85</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P2A_R-Edad-trans_bre.xlsx
+++ b/data/trans_bre/P2A_R-Edad-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-13,14; 8,78</t>
+          <t>-13,4; 9,04</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-13,75; 6,6</t>
+          <t>-14,47; 6,69</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-15,07; 4,92</t>
+          <t>-15,36; 4,6</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-3,65; 17,47</t>
+          <t>-3,67; 16,61</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-35,45; 34,86</t>
+          <t>-36,66; 33,02</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-34,72; 23,02</t>
+          <t>-37,01; 22,8</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-41,21; 19,29</t>
+          <t>-41,64; 19,13</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-4,14; 24,08</t>
+          <t>-4,24; 22,55</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-12,37; 2,69</t>
+          <t>-12,38; 2,86</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-2,92; 13,23</t>
+          <t>-3,28; 13,34</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-7,71; 7,61</t>
+          <t>-8,27; 7,39</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-8,86; 7,08</t>
+          <t>-9,07; 6,17</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-32,56; 8,57</t>
+          <t>-31,18; 9,89</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-8,58; 50,97</t>
+          <t>-11,01; 52,63</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-23,26; 30,19</t>
+          <t>-24,47; 28,85</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-11,11; 9,56</t>
+          <t>-11,17; 8,33</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-15,39; 8,69</t>
+          <t>-14,78; 8,31</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-11,43; 11,83</t>
+          <t>-10,7; 11,6</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-13,88; 5,65</t>
+          <t>-13,74; 5,13</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-4,26; 11,94</t>
+          <t>-3,89; 11,49</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-33,74; 24,18</t>
+          <t>-32,67; 24,9</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-24,5; 35,98</t>
+          <t>-23,82; 33,85</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-32,97; 18,25</t>
+          <t>-33,1; 15,68</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-5,36; 16,54</t>
+          <t>-4,85; 16,05</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-15,12; 3,14</t>
+          <t>-15,21; 3,37</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-13,42; 7,34</t>
+          <t>-13,37; 7,99</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,68; 22,2</t>
+          <t>-0,3; 21,18</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-6,57; 14,26</t>
+          <t>-7,31; 12,74</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-32,71; 8,1</t>
+          <t>-33,62; 9,27</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-29,06; 22,15</t>
+          <t>-30,39; 22,77</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>3,87; 74,96</t>
+          <t>-0,58; 70,94</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-8,79; 21,41</t>
+          <t>-9,1; 19,18</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-9,33; -0,18</t>
+          <t>-8,94; 0,45</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-4,85; 4,83</t>
+          <t>-4,79; 5,31</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-4,17; 5,38</t>
+          <t>-3,83; 5,72</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-2,63; 7,88</t>
+          <t>-2,77; 7,81</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-23,34; -0,03</t>
+          <t>-22,7; 1,33</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-12,81; 14,58</t>
+          <t>-12,64; 16,28</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-11,57; 17,29</t>
+          <t>-10,79; 18,44</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-3,38; 10,85</t>
+          <t>-3,51; 10,78</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P2A_R-Edad-trans_bre.xlsx
+++ b/data/trans_bre/P2A_R-Edad-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>5,91</t>
+          <t>4,79</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>7,3%</t>
+          <t>5,85%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-13,4; 9,04</t>
+          <t>-12,35; 10,28</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-14,47; 6,69</t>
+          <t>-14,48; 6,41</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-15,36; 4,6</t>
+          <t>-14,77; 5,26</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-3,67; 16,61</t>
+          <t>-4,29; 15,86</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-36,66; 33,02</t>
+          <t>-34,54; 42,38</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-37,01; 22,8</t>
+          <t>-36,34; 21,6</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-41,64; 19,13</t>
+          <t>-40,61; 21,01</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-4,24; 22,55</t>
+          <t>-4,96; 21,31</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>-0,96</t>
+          <t>-3,18</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>-1,23%</t>
+          <t>-4,03%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-12,38; 2,86</t>
+          <t>-11,68; 3,96</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-3,28; 13,34</t>
+          <t>-3,87; 12,82</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-8,27; 7,39</t>
+          <t>-8,98; 6,77</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-9,07; 6,17</t>
+          <t>-11,48; 4,57</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-31,18; 9,89</t>
+          <t>-30,5; 12,77</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-11,01; 52,63</t>
+          <t>-11,48; 50,69</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-24,47; 28,85</t>
+          <t>-27,29; 24,88</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-11,17; 8,33</t>
+          <t>-14,12; 5,98</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>4,0</t>
+          <t>4,07</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>5,29%</t>
+          <t>5,37%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-14,78; 8,31</t>
+          <t>-14,86; 8,57</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-10,7; 11,6</t>
+          <t>-10,59; 11,95</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-13,74; 5,13</t>
+          <t>-13,61; 5,55</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-3,89; 11,49</t>
+          <t>-3,54; 11,5</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-32,67; 24,9</t>
+          <t>-33,2; 24,23</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-23,82; 33,85</t>
+          <t>-23,78; 35,24</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-33,1; 15,68</t>
+          <t>-33,07; 17,77</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-4,85; 16,05</t>
+          <t>-4,43; 16,26</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>2,16</t>
+          <t>-0,76</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>-1,0%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-15,21; 3,37</t>
+          <t>-16,28; 2,23</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-13,37; 7,99</t>
+          <t>-13,09; 5,99</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-0,3; 21,18</t>
+          <t>0,05; 21,08</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-7,31; 12,74</t>
+          <t>-8,3; 8,06</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-33,62; 9,27</t>
+          <t>-34,86; 5,93</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-30,39; 22,77</t>
+          <t>-29,03; 17,16</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-0,58; 70,94</t>
+          <t>0,44; 68,59</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-9,1; 19,18</t>
+          <t>-10,35; 11,54</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>2,22</t>
+          <t>0,57</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>0,74%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-8,94; 0,45</t>
+          <t>-9,27; 0,33</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-4,79; 5,31</t>
+          <t>-4,78; 5,1</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-3,83; 5,72</t>
+          <t>-4,09; 5,22</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-2,77; 7,81</t>
+          <t>-3,56; 5,22</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-22,7; 1,33</t>
+          <t>-23,54; 1,02</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-12,64; 16,28</t>
+          <t>-12,67; 15,46</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-10,79; 18,44</t>
+          <t>-11,5; 16,36</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-3,51; 10,78</t>
+          <t>-4,55; 6,81</t>
         </is>
       </c>
     </row>
